--- a/artfynd/A 33678-2025 artfynd.xlsx
+++ b/artfynd/A 33678-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112550305</v>
+        <v>112550310</v>
       </c>
       <c r="B2" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526238</v>
+        <v>526183</v>
       </c>
       <c r="R2" t="n">
-        <v>6984989</v>
+        <v>6984936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112550307</v>
+        <v>112550312</v>
       </c>
       <c r="B3" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526429</v>
+        <v>526198</v>
       </c>
       <c r="R3" t="n">
-        <v>6984852</v>
+        <v>6984921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,37 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112550306</v>
+        <v>112550307</v>
       </c>
       <c r="B4" t="n">
-        <v>90934</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526335</v>
+        <v>526429</v>
       </c>
       <c r="R4" t="n">
-        <v>6984934</v>
+        <v>6984852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,6 +1007,684 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112550306</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rundeln, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>526335</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6984934</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112550308</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rundeln, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>526147</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6984955</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112550305</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rundeln, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>526238</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6984989</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112550309</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rundeln, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>526186</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6984928</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112550311</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rundeln, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>526186</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6984926</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112550303</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rundeln, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>526203</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6985029</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 33678-2025 artfynd.xlsx
+++ b/artfynd/A 33678-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550307</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550306</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550308</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550305</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550309</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,8 +1734,24 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550311</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>